--- a/261023_보고서_소울푸드방문결과.xlsx
+++ b/261023_보고서_소울푸드방문결과.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>베트남 광닌 공장 직수입(거래 약 3년 반). 설비(X-ray 등)·베트남 HACCP·ISO 보유. 30g은 사옹원 강세·단가 경쟁이라 50g으로 차별화. 감자채전 월 약 1만 박스, 김치전·녹두전 성장 중</t>
+          <t>베트남 광닌 공장 직수입(거래 약 3년 반). 설비(X-ray 등)·베트남 HACCP·ISO 보유. 30g은 사옹원 강세·단가 경쟁이라 50g으로 차별화. 소울푸드 전체 매출 월 약 4억 원. 감자채전 월 약 1만 박스, 김치전·녹두전 성장 중</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>서울 급식은 렌시푸드가 권한 보유. CJ프레시원은 대구센터만 입고(양산 코드 개방, 물량 적을 전망). 아워홈 입고 확실. 중·고교 급식 호조, 군납은 단가 위주라 부진</t>
+          <t>랜시푸드가 총판권 보유, 아워홈에 공급 중(월 약 1.5억 원, 소울푸드 전체 월 약 4억 원의 약 38%). CJ프레시원은 대구센터만 입고(양산 코드 개방, 물량 적을 전망). 중·고교 급식 호조, 군납은 단가 위주라 부진</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -752,7 +752,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>단가가 높은 편이라 원가 경쟁력 확인 필요. 렌시푸드와 권한 중복 가능성 → 교통정리 선행 필요. 온라인은 총판이 운영 중이라 진입 여지 적음. 우리 도매 조직 없음</t>
+          <t>단가가 높은 편이라 원가 경쟁력 확인 필요. 랜시푸드 총판권·아워홈 공급과 판매권이 겹쳐 정리가 선행 필요(소울푸드가 차주 수요일 10/28 진행 예정). 온라인은 총판이 운영 중이라 진입 여지 적음. 우리 도매 조직 없음</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
@@ -841,7 +841,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>렌시 의견 확인(소울푸드 대표가 수요일 푸디스트 방문 시 문의)</t>
+          <t>판매권(총판권) 정리 결과 확인 — 소울푸드가 랜시푸드와 조율(푸디스트 담당자 방문 시 문의 포함)</t>
         </is>
       </c>
       <c r="C26" s="10" t="n"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>수요일</t>
+          <t>10/28(수)</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       <c r="A30" s="12" t="inlineStr">
         <is>
           <t>· 방문 장소·시간, 참석자 이름(녹취는 "참석자 1~4"로만 표기)
-· 렌시푸드 매출 "1억 5천"이 월/연 어느 쪽인지, 웰스토리 경유 업체명(녹취 불명확)
+· 웰스토리 경유 업체명(녹취 불명확), 매출은 구두 언급 수치(랜시 월 약 1.5억·소울푸드 전체 월 약 4억)
 · 단가·MOQ 수치는 이번 미팅에서 논의되지 않음</t>
         </is>
       </c>

--- a/261023_보고서_소울푸드방문결과.xlsx
+++ b/261023_보고서_소울푸드방문결과.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보고서" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'보고서'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'보고서'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,12 +39,12 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -69,22 +69,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00888888"/>
-      </left>
-      <right style="thin">
-        <color rgb="00888888"/>
-      </right>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00888888"/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
       </bottom>
     </border>
     <border>
-      <bottom style="medium">
-        <color rgb="00000000"/>
+      <left style="thin">
+        <color rgb="00888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="00888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00888888"/>
       </bottom>
     </border>
     <border>
@@ -135,31 +135,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -530,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -547,349 +543,327 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>작성일: 2026-10-23
-영업2본부 케이터링팀 / 이영진
-수신: 팀장님</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+          <t>작성일: 2026-10-23   |   영업2본부 케이터링팀 / 이영진   |   수신: 팀장님</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1. 방문 개요</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>일시·방문처</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22 / 소울푸드(수입원·유통전문판매원, 직원 3명)  ※ 장소·시간 확인 필요</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>참석</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>이영진(팀장님 대신 참석) 외 우리 측 3명(이름 확인 필요), 소울푸드 대표</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>베트남산 50g 전류·튀김(브랜드 월남간) 도입 가능성 및 공급 조건 확인</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2. 주요 내용</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="51" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>업체·제품</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>베트남 광닌 공장 직수입(거래 약 3년 반). 설비(X-ray 등)·베트남 HACCP·ISO 보유. 30g은 사옹원 강세·단가 경쟁이라 50g으로 차별화. 소울푸드 전체 매출 월 약 4억 원. 감자채전 월 약 1만 박스, 김치전·녹두전 성장 중</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>신제품·일정</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>12월 컨테이너로 녹두전·감자채전 250g×4장(1kg) 첫 통관. 샘플 예정: 크런치 오징어튀김·치즈볼·감자채튀김·야채고로케(유탕)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="51" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>유통 현황</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>랜시푸드가 총판권 보유, 아워홈에 공급 중(월 약 1.5억 원, 소울푸드 전체 월 약 4억 원의 약 38%). CJ프레시원은 대구센터만 입고(양산 코드 개방, 물량 적을 전망). 중·고교 급식 호조, 군납은 단가 위주라 부진</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="51" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>도입 조건</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>우리 전용 스티커·포장으로 수입 가능(수입필증으로 HACCP 인정). 100박스(1kg×5봉) 시험 통관 제안, 샘플 아이스박스 제공. 단가·MOQ는 미논의(전체 견적 요청 예정). 판매가 준수 요구</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>물류</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>CJ대한통운 냉동 물류와 10/23 미팅 예정. 30~50박스부터 배송 가능 여부 협의(과거 약 210박스 이상 조건)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="8" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3. 검토 의견 (안)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>기회</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>50g·품질 차별화로 학교·단체급식 수요 기대. 월남간 외 신제품(치즈볼·칠리오징어 등) 단독 공급 제안 가능</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="51" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>우려</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>단가가 높은 편이라 원가 경쟁력 확인 필요. 랜시푸드 총판권·아워홈 공급과 판매권이 겹쳐 정리가 선행 필요(소울푸드가 차주 수요일 10/28 진행 예정). 온라인은 총판이 운영 중이라 진입 여지 적음. 우리 도매 조직 없음</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="8" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>4. 향후 계획 (안)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>담당</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>팀장</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>본부장</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>1. 방문 개요</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>일시·방문처</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-22 / 소울푸드(수입원·유통전문판매원, 직원 3명)  ※ 장소·시간 확인 필요</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="10" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>참석</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>이영진(팀장님 대신 참석) 외 우리 측 3명(이름 확인 필요), 소울푸드 대표</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>목적</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>베트남산 50g 전류·튀김(브랜드 월남간) 도입 가능성 및 공급 조건 확인</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="10" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2. 주요 내용</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="51" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>업체·제품</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>베트남 광닌 공장 직수입(거래 약 3년 반). 설비(X-ray 등)·베트남 HACCP·ISO 보유. 30g은 사옹원 강세·단가 경쟁이라 50g으로 차별화. 소울푸드 전체 매출 월 약 4억 원. 감자채전 월 약 1만 박스, 김치전·녹두전 성장 중</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>신제품·일정</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>12월 컨테이너로 녹두전·감자채전 250g×4장(1kg) 첫 통관. 샘플 예정: 크런치 오징어튀김·치즈볼·감자채튀김·야채고로케(유탕)</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="51" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>유통 현황</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>랜시푸드가 총판권 보유, 아워홈에 공급 중(월 약 1.5억 원, 소울푸드 전체 월 약 4억 원의 약 38%). CJ프레시원은 대구센터만 입고(양산 코드 개방, 물량 적을 전망). 중·고교 급식 호조, 군납은 단가 위주라 부진</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="51" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>도입 조건</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>우리 전용 스티커·포장으로 수입 가능(수입필증으로 HACCP 인정). 100박스(1kg×5봉) 시험 통관 제안, 샘플 아이스박스 제공. 단가·MOQ는 미논의(전체 견적 요청 예정). 판매가 준수 요구</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>물류</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>CJ대한통운 냉동 물류와 10/23 미팅 예정. 30~50박스부터 배송 가능 여부 협의(과거 약 210박스 이상 조건)</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="10" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>3. 검토 의견 (안)</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>기회</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>50g·품질 차별화로 학교·단체급식 수요 기대. 월남간 외 신제품(치즈볼·칠리오징어 등) 단독 공급 제안 가능</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="51" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>우려</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>단가가 높은 편이라 원가 경쟁력 확인 필요. 랜시푸드 총판권·아워홈 공급과 판매권이 겹쳐 정리가 선행 필요(소울푸드가 차주 수요일 10/28 진행 예정). 온라인은 총판이 운영 중이라 진입 여지 적음. 우리 도매 조직 없음</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="10" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>4. 향후 계획 (안)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>담당</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>기한</t>
         </is>
       </c>
     </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>소울푸드에 전체 견적·단가·MOQ·판매 금지 채널·권장 판가 요청</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>이영진</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+    </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>소울푸드에 전체 견적·단가·MOQ·판매 금지 채널·권장 판가 요청</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>각 MD(웰스토리·아워홈·현대그린푸드·푸드머스·푸디스트·CJ프레시웨이·동원·신세계) 50g 수요 확인</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>이영진</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>각 MD(웰스토리·아워홈·현대그린푸드·푸드머스·푸디스트·CJ프레시웨이·동원·신세계) 50g 수요 확인</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>판매권(총판권) 정리 결과 확인 — 소울푸드가 랜시푸드와 조율(푸디스트 담당자 방문 시 문의 포함)</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>소울푸드 대표</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>10/28(수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>샘플 수령·시식 후 결과를 정리해 팀장님께 재보고</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>이영진</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>판매권(총판권) 정리 결과 확인 — 소울푸드가 랜시푸드와 조율(푸디스트 담당자 방문 시 문의 포함)</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>소울푸드 대표</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>10/28(수)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>샘플 수령·시식 후 결과를 정리해 팀장님께 재보고</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>이영진</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>5. 확인 필요</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>· 방문 장소·시간, 참석자 이름(녹취는 "참석자 1~4"로만 표기)
 · 웰스토리 경유 업체명(녹취 불명확), 매출은 구두 언급 수치(랜시 월 약 1.5억·소울푸드 전체 월 약 4억)
@@ -899,29 +873,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="B9:E9"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B6:E6"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B16:E16"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A3:B4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
